--- a/output/full_scan/batch_seq7_2026-07-03.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-03.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6491</v>
+        <v>6488</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>854</v>
+        <v>858.6531634735169</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>372.5</v>
+        <v>1255</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>78.21434440626595</v>
+        <v>68.47475366354998</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.29997794822822</v>
+        <v>23.30796839035107</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.287746137653929</v>
+        <v>0.8781278324256122</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.403693111337287</v>
+        <v>16.18633309230704</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6525</v>
+        <v>6491</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>846.6349369028156</v>
+        <v>854</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>183</v>
+        <v>372.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.33599597595558</v>
+        <v>78.21434440626595</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>36.47758773022751</v>
+        <v>29.29997794822822</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.370737727804786</v>
+        <v>6.287746137653929</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.301631793520238</v>
+        <v>3.403693111337287</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6486</v>
+        <v>6525</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>833.4691512259847</v>
+        <v>846.6349369028156</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>83.5</v>
+        <v>183</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.12210241057045</v>
+        <v>73.33599597595558</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.61630958318669</v>
+        <v>36.47758773022751</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.792526277059922</v>
+        <v>2.370737727804786</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2155275328081476</v>
+        <v>2.301631793520238</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6754</v>
+        <v>6486</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>817.8229595238994</v>
+        <v>833.4691512259847</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46.3</v>
+        <v>83.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>61.28314355453411</v>
+        <v>59.12210241057045</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18.82645688557084</v>
+        <v>15.61630958318669</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.882295952389939</v>
+        <v>1.792526277059922</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0734658351239167</v>
+        <v>0.2155275328081476</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6794</v>
+        <v>6754</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>737.5479030629332</v>
+        <v>817.8229595238994</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.35333647246513</v>
+        <v>61.28314355453411</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16.5368266566204</v>
+        <v>18.82645688557084</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.754643274620096</v>
+        <v>4.882295952389939</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1747012514570209</v>
+        <v>0.0734658351239167</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6782</v>
+        <v>6794</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>737.4427273950899</v>
+        <v>737.5479030629332</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>209.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.91542173088195</v>
+        <v>60.35333647246513</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10.67393319559071</v>
+        <v>16.5368266566204</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.594630835098084</v>
+        <v>3.754643274620096</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.579057021516668</v>
+        <v>0.1747012514570209</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6505</v>
+        <v>6782</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>729.6179004166438</v>
+        <v>737.4427273950899</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>58.9</v>
+        <v>209.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.04037134690996</v>
+        <v>65.91542173088195</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.56414370443258</v>
+        <v>10.67393319559071</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.561790041664386</v>
+        <v>3.594630835098084</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4793976799934251</v>
+        <v>1.579057021516668</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6753</v>
+        <v>6505</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>727.3249883542119</v>
+        <v>729.6179004166438</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>154</v>
+        <v>58.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>75.21944542815363</v>
+        <v>63.04037134690996</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.3589950472015</v>
+        <v>15.56414370443258</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.832498835421186</v>
+        <v>3.561790041664386</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.372690117632956</v>
+        <v>0.4793976799934251</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6666</v>
+        <v>6753</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>724.2355297597298</v>
+        <v>727.3249883542119</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>43.85</v>
+        <v>154</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.95580880961751</v>
+        <v>75.21944542815363</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44.30637131906236</v>
+        <v>22.3589950472015</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6125630444750114</v>
+        <v>2.832498835421186</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0123914659987404</v>
+        <v>3.372690117632956</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6556</v>
+        <v>6666</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>692.1560931442863</v>
+        <v>724.2355297597298</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>71.5</v>
+        <v>43.85</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>48.61873862134554</v>
+        <v>60.95580880961751</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.83090147782373</v>
+        <v>44.30637131906236</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.564450686641698</v>
+        <v>0.6125630444750114</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.2298065475404839</v>
+        <v>0.0123914659987404</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6742</v>
+        <v>6693</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>670.5191518647082</v>
+        <v>695.1953770221318</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>251.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.56825863449895</v>
+        <v>69.38202826136765</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33.37439073720545</v>
+        <v>50.29919486318715</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6382730962095744</v>
+        <v>0.3004826828767002</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.5445582739589856</v>
+        <v>2.681322062214541</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6573</v>
+        <v>6556</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>664.692057013247</v>
+        <v>692.1560931442863</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>25.1</v>
+        <v>71.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>76.50569629392292</v>
+        <v>48.61873862134554</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.53514987145911</v>
+        <v>28.83090147782373</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.359705388292257</v>
+        <v>1.564450686641698</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.6193123445751836</v>
+        <v>-0.2298065475404839</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6585</v>
+        <v>6742</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>659.2699984908802</v>
+        <v>670.5191518647082</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>134.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.39470925523205</v>
+        <v>57.56825863449895</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>48.11443229585012</v>
+        <v>33.37439073720545</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5566450344069218</v>
+        <v>0.6382730962095744</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-2.049745525202765</v>
+        <v>-0.5445582739589856</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6531</v>
+        <v>6573</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>659.1173781517632</v>
+        <v>664.692057013247</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>987</v>
+        <v>25.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>49.89534047186062</v>
+        <v>76.50569629392292</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.40118041649207</v>
+        <v>28.53514987145911</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.81395378930472</v>
+        <v>2.359705388292257</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-8.523000476404816</v>
+        <v>0.6193123445751836</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6515</v>
+        <v>6585</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>656.624638885849</v>
+        <v>659.2699984908802</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9900</v>
+        <v>134.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.6760645059641</v>
+        <v>61.39470925523205</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.04971757250053</v>
+        <v>48.11443229585012</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.471419745275084</v>
+        <v>0.5566450344069218</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>46.63072084063191</v>
+        <v>-2.049745525202765</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6658</v>
+        <v>6531</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>651.7425667997408</v>
+        <v>659.1173781517632</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>208.5</v>
+        <v>987</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.0522643711696</v>
+        <v>49.89534047186062</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.15339612543871</v>
+        <v>23.40118041649207</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.801038494215417</v>
+        <v>0.81395378930472</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.551235359046261</v>
+        <v>-8.523000476404816</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6613</v>
+        <v>6515</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>647.7517059091558</v>
+        <v>656.624638885849</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>360</v>
+        <v>9900</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.33924068114664</v>
+        <v>58.6760645059641</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.91191407579215</v>
+        <v>17.04971757250053</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6507749239061167</v>
+        <v>1.471419745275084</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.004266275957484</v>
+        <v>46.63072084063191</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6672</v>
+        <v>6658</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>645.8349210069364</v>
+        <v>651.7425667997408</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>315</v>
+        <v>208.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>73.54135480826046</v>
+        <v>53.0522643711696</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>41.80280605683598</v>
+        <v>30.15339612543871</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8876021722715697</v>
+        <v>1.801038494215417</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.041724668961745</v>
+        <v>2.551235359046261</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6691</v>
+        <v>6613</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>644.1607472665472</v>
+        <v>647.7517059091558</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>762</v>
+        <v>360</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.0791598784645</v>
+        <v>61.33924068114664</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.52194335720844</v>
+        <v>31.91191407579215</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.781280691435261</v>
+        <v>0.6507749239061167</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.935844348586926</v>
+        <v>-1.004266275957484</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6757</v>
+        <v>6672</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>633.4836010075858</v>
+        <v>645.8349210069364</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>60.5</v>
+        <v>315</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.6003483121232</v>
+        <v>73.54135480826046</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>36.52447474319906</v>
+        <v>41.80280605683598</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4019763799917692</v>
+        <v>0.8876021722715697</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0526589666011092</v>
+        <v>5.041724668961745</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6548</v>
+        <v>6691</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>633.1070707179053</v>
+        <v>644.1607472665472</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>762</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.33851254267491</v>
+        <v>60.0791598784645</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>38.91895536187437</v>
+        <v>31.52194335720844</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.073368945141284</v>
+        <v>0.781280691435261</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.245364114058332</v>
+        <v>1.935844348586926</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6781</v>
+        <v>6757</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>630.8836545919407</v>
+        <v>633.4836010075858</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1225</v>
+        <v>60.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.58946863077156</v>
+        <v>55.6003483121232</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11.12922090246394</v>
+        <v>36.52447474319906</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9223290986779332</v>
+        <v>0.4019763799917692</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>5.57549504803982</v>
+        <v>-0.0526589666011092</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6790</v>
+        <v>6548</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>615.0959055159299</v>
+        <v>633.1070707179053</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>40.85</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.03986002529761</v>
+        <v>61.33851254267491</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.82387447907493</v>
+        <v>38.91895536187437</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.199787043240478</v>
+        <v>2.073368945141284</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.08425815696902809</v>
+        <v>-1.245364114058332</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6589</v>
+        <v>6781</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>606.2148766678765</v>
+        <v>630.8836545919407</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>49.7</v>
+        <v>1225</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>61.8202646295971</v>
+        <v>56.58946863077156</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.4747867367518</v>
+        <v>11.12922090246394</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.282247724142454</v>
+        <v>0.9223290986779332</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3789503845600986</v>
+        <v>5.57549504803982</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6651</v>
+        <v>6790</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>604.1356879394901</v>
+        <v>615.0959055159299</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>162</v>
+        <v>40.85</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>61.15480865299396</v>
+        <v>62.03986002529761</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>30.1045843005298</v>
+        <v>25.82387447907493</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.131888165373594</v>
+        <v>1.199787043240478</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3767224266108542</v>
+        <v>0.08425815696902809</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6684</v>
+        <v>6589</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>594.749329997043</v>
+        <v>606.2148766678765</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>59</v>
+        <v>49.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.28801372581283</v>
+        <v>61.8202646295971</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>39.34822057882264</v>
+        <v>21.4747867367518</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6205927382268192</v>
+        <v>1.282247724142454</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.3639013733161422</v>
+        <v>0.3789503845600986</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6494</v>
+        <v>6651</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>592.5288435792987</v>
+        <v>604.1356879394901</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>62.32507047189569</v>
+        <v>61.15480865299396</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.9874254172917</v>
+        <v>30.1045843005298</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.510500484041981</v>
+        <v>1.131888165373594</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0681326533999837</v>
+        <v>0.3767224266108542</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6667</v>
+        <v>6684</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>591.8893855086798</v>
+        <v>594.749329997043</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>271</v>
+        <v>59</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.27092177453398</v>
+        <v>58.28801372581283</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10.43681200281458</v>
+        <v>39.34822057882264</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3580045968765624</v>
+        <v>0.6205927382268192</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.072403450773817</v>
+        <v>0.3639013733161422</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6582</v>
+        <v>6494</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>591.3059063186145</v>
+        <v>592.5288435792987</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>33.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>68.35634198852236</v>
+        <v>62.32507047189569</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>35.06037109375197</v>
+        <v>32.9874254172917</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6455450682343858</v>
+        <v>0.510500484041981</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1186355289872083</v>
+        <v>-0.0681326533999837</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6719</v>
+        <v>6667</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>585.2216617461643</v>
+        <v>591.8893855086798</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.09377551463322</v>
+        <v>51.27092177453398</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>38.7973542247093</v>
+        <v>10.43681200281458</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.122166174616429</v>
+        <v>0.3580045968765624</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.029123704015646</v>
+        <v>-1.072403450773817</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6668</v>
+        <v>6582</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>582.3781735057744</v>
+        <v>591.3059063186145</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>39.9</v>
+        <v>33.4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.74151306119236</v>
+        <v>68.35634198852236</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.41136652352288</v>
+        <v>35.06037109375197</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3525229849030253</v>
+        <v>0.6455450682343858</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.4890165313590073</v>
+        <v>0.1186355289872083</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6625</v>
+        <v>6719</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>555.5870564620252</v>
+        <v>585.2216617461643</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>60.76579789713997</v>
+        <v>61.09377551463322</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.34581809830829</v>
+        <v>38.7973542247093</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9410754248710096</v>
+        <v>1.122166174616429</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0107660657609434</v>
+        <v>2.029123704015646</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6645</v>
+        <v>6668</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>552.6659049365237</v>
+        <v>582.3781735057744</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>15.55</v>
+        <v>39.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.25460108497765</v>
+        <v>49.74151306119236</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>50.26647483360715</v>
+        <v>21.41136652352288</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.1625425490638257</v>
+        <v>0.3525229849030253</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,48 +2425,48 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0202490223148398</v>
+        <v>-0.4890165313590073</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6806</v>
+        <v>6625</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>548.7768356926886</v>
+        <v>555.5870564620252</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3.51</v>
+        <v>79</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>31.69502817351714</v>
+        <v>60.76579789713997</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>32.59319613389467</v>
+        <v>29.34581809830829</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.9410754248710096</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4112821528792731</v>
+        <v>0.0107660657609434</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6517</v>
+        <v>6645</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>533.2672348212973</v>
+        <v>552.6659049365237</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>71.3</v>
+        <v>15.55</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.0375417826945</v>
+        <v>59.25460108497765</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29.54609227692899</v>
+        <v>50.26647483360715</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.353751801144801</v>
+        <v>0.1625425490638257</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,48 +2531,48 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.6624253726256599</v>
+        <v>-0.0202490223148398</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6654</v>
+        <v>6806</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>532.1631644456426</v>
+        <v>548.7768356926886</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>200</v>
+        <v>3.51</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G40" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>65.5052472082981</v>
+        <v>31.69502817351714</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>44.0099042959412</v>
+        <v>32.59319613389467</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6484677408576881</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-3.760476717482874</v>
+        <v>0.4112821528792731</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6538</v>
+        <v>6517</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>527.6626740989346</v>
+        <v>533.2672348212973</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>135.5</v>
+        <v>71.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>60.25654172948202</v>
+        <v>54.0375417826945</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>34.14665191603606</v>
+        <v>29.54609227692899</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.366541011150689</v>
+        <v>0.353751801144801</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.322111595971379</v>
+        <v>-0.6624253726256599</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6640</v>
+        <v>6654</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>520.2929833924539</v>
+        <v>532.1631644456426</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1125</v>
+        <v>200</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.04765216972524</v>
+        <v>65.5052472082981</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.75298659854212</v>
+        <v>44.0099042959412</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.906013747597508</v>
+        <v>0.6484677408576881</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>18.71383964601741</v>
+        <v>-3.760476717482874</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6716</v>
+        <v>6538</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>509.984474616753</v>
+        <v>527.6626740989346</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>99.5</v>
+        <v>135.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.3059476127096</v>
+        <v>60.25654172948202</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.20264809074565</v>
+        <v>34.14665191603606</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7974431410904088</v>
+        <v>2.366541011150689</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.343354569662161</v>
+        <v>1.322111595971379</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6643</v>
+        <v>6640</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>506.2427796507575</v>
+        <v>520.2929833924539</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>511</v>
+        <v>1125</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.57022069016206</v>
+        <v>48.04765216972524</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.41982882002496</v>
+        <v>21.75298659854212</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.922827110749366</v>
+        <v>1.906013747597508</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>4.641888698037771</v>
+        <v>18.71383964601741</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6831</v>
+        <v>6716</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>504.3147046126459</v>
+        <v>509.984474616753</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>923</v>
+        <v>99.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>64.59239305900537</v>
+        <v>54.3059476127096</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>29.97827938503222</v>
+        <v>19.20264809074565</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8372620501897642</v>
+        <v>0.7974431410904088</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>10.49854194140181</v>
+        <v>-0.343354569662161</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6579</v>
+        <v>6643</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>501.9084307519079</v>
+        <v>506.2427796507575</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>165.5</v>
+        <v>511</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.68611263285549</v>
+        <v>50.57022069016206</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.06449348376465</v>
+        <v>20.41982882002496</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7444259640536045</v>
+        <v>1.922827110749366</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.8055257343223725</v>
+        <v>4.641888698037771</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6642</v>
+        <v>6831</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>500.1257390697333</v>
+        <v>504.3147046126459</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>923</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.77513626119001</v>
+        <v>64.59239305900537</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>33.39779640994952</v>
+        <v>29.97827938503222</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2973320817113447</v>
+        <v>0.8372620501897642</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.023373929263657</v>
+        <v>10.49854194140181</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6584</v>
+        <v>6579</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>499.2895245598974</v>
+        <v>501.9084307519079</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>707</v>
+        <v>165.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.25837389306218</v>
+        <v>57.68611263285549</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.45305563387974</v>
+        <v>21.06449348376465</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7531867459139125</v>
+        <v>0.7444259640536045</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>9.462680645080534</v>
+        <v>-0.8055257343223725</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6799</v>
+        <v>6642</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>495.136740148129</v>
+        <v>500.1257390697333</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>101.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.68927186433287</v>
+        <v>51.77513626119001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.8884514290667</v>
+        <v>33.39779640994952</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6714640931377533</v>
+        <v>0.2973320817113447</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2154480256885245</v>
+        <v>-1.023373929263657</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6727</v>
+        <v>6584</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>490.5096350866394</v>
+        <v>499.2895245598974</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>445</v>
+        <v>707</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.82546214244163</v>
+        <v>54.25837389306218</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12.80273391073076</v>
+        <v>16.45305563387974</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.620135034526564</v>
+        <v>0.7531867459139125</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.105173534251403</v>
+        <v>9.462680645080534</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6770</v>
+        <v>6799</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>490.4496173204092</v>
+        <v>495.136740148129</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.95925102215914</v>
+        <v>54.68927186433287</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.53766292174992</v>
+        <v>22.8884514290667</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4820556676920608</v>
+        <v>0.6714640931377533</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.786665072787935</v>
+        <v>0.2154480256885245</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6669</v>
+        <v>6727</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>484.6607124974373</v>
+        <v>490.5096350866394</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>5265</v>
+        <v>445</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.52351926438836</v>
+        <v>49.82546214244163</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.22112109710203</v>
+        <v>12.80273391073076</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8265185518427054</v>
+        <v>0.620135034526564</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>38.0073363040637</v>
+        <v>1.105173534251403</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6526</v>
+        <v>6770</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>483.2516575036948</v>
+        <v>490.4496173204092</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>706</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>56.78674722288976</v>
+        <v>48.95925102215914</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.53649434064382</v>
+        <v>21.53766292174992</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.898196041633282</v>
+        <v>0.4820556676920608</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.472950606681477</v>
+        <v>-0.786665072787935</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6725</v>
+        <v>6683</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>481.67837713556</v>
+        <v>490.2194508516177</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>340</v>
+        <v>1805</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.88460893941408</v>
+        <v>53.8532722620677</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.9115764665594</v>
+        <v>14.71213043287215</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2544423881434456</v>
+        <v>0.2429403459795713</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>2.165014662008842</v>
+        <v>22.0559306551394</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6568</v>
+        <v>6669</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>474.8889651881195</v>
+        <v>484.6607124974373</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>162.5</v>
+        <v>5265</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>35.03175859451761</v>
+        <v>57.52351926438836</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>34.52049262649405</v>
+        <v>16.22112109710203</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3890956967139198</v>
+        <v>0.8265185518427054</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0956541331246878</v>
+        <v>38.0073363040637</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6560</v>
+        <v>6526</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>459.890408752659</v>
+        <v>483.2516575036948</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>40.25</v>
+        <v>706</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>59.58131401489118</v>
+        <v>56.78674722288976</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.8250242763214</v>
+        <v>14.53649434064382</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7120508259066687</v>
+        <v>0.898196041633282</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2055032567958306</v>
+        <v>2.472950606681477</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6614</v>
+        <v>6725</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>453.5719058760886</v>
+        <v>481.67837713556</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>40.4</v>
+        <v>340</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.36665073022522</v>
+        <v>54.88460893941408</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.56533236645154</v>
+        <v>24.9115764665594</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.932889278213626</v>
+        <v>0.2544423881434456</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0171351955146804</v>
+        <v>2.165014662008842</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6698</v>
+        <v>6568</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>453.5575849234688</v>
+        <v>474.8889651881195</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>41.2</v>
+        <v>162.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.48484008128643</v>
+        <v>35.03175859451761</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>31.74647321193794</v>
+        <v>34.52049262649405</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.370211225365967</v>
+        <v>0.3890956967139198</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.436064596078177</v>
+        <v>0.0956541331246878</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6588</v>
+        <v>6560</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>452.071337596616</v>
+        <v>459.890408752659</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>40.25</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>34.36204888924541</v>
+        <v>59.58131401489118</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.9025253041315</v>
+        <v>27.8250242763214</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7864701719533099</v>
+        <v>0.7120508259066687</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.7914098575043873</v>
+        <v>0.2055032567958306</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6695</v>
+        <v>6614</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>450.5974057651045</v>
+        <v>453.5719058760886</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>58.1</v>
+        <v>40.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.60424526122508</v>
+        <v>54.36665073022522</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25.00634375820114</v>
+        <v>18.56533236645154</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3667573491552451</v>
+        <v>0.932889278213626</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3615454684431252</v>
+        <v>0.0171351955146804</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6743</v>
+        <v>6698</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>446.1359289332847</v>
+        <v>453.5575849234688</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>31.3</v>
+        <v>41.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>60.58925522843776</v>
+        <v>51.48484008128643</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>28.99116419217913</v>
+        <v>31.74647321193794</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.546576566450055</v>
+        <v>0.370211225365967</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.160870687828613</v>
+        <v>-0.436064596078177</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6641</v>
+        <v>6588</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>438.4351993133702</v>
+        <v>452.071337596616</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>18.4</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.22143330677331</v>
+        <v>34.36204888924541</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.84696594622631</v>
+        <v>19.9025253041315</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9435199313370208</v>
+        <v>0.7864701719533099</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0065450367121037</v>
+        <v>-0.7914098575043873</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6664</v>
+        <v>6695</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>435.4739131736431</v>
+        <v>450.5974057651045</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>395.5</v>
+        <v>58.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.44540258681773</v>
+        <v>51.60424526122508</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.02468010761978</v>
+        <v>25.00634375820114</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8085355914330724</v>
+        <v>0.3667573491552451</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>3.816741347240294</v>
+        <v>-0.3615454684431252</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6510</v>
+        <v>6743</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>431.9468980332318</v>
+        <v>446.1359289332847</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>3320</v>
+        <v>31.3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.99334809676097</v>
+        <v>60.58925522843776</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.91817181243905</v>
+        <v>28.99116419217913</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4280805604603976</v>
+        <v>0.546576566450055</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-19.1046736389584</v>
+        <v>0.160870687828613</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6670</v>
+        <v>6641</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>430.5053902882127</v>
+        <v>438.4351993133702</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>259</v>
+        <v>18.4</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.48323280946506</v>
+        <v>53.22143330677331</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.7873940314838</v>
+        <v>14.84696594622631</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4470325742187998</v>
+        <v>0.9435199313370208</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.901989469333766</v>
+        <v>0.0065450367121037</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6803</v>
+        <v>6664</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>429.4164385005847</v>
+        <v>435.4739131736431</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>279</v>
+        <v>395.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33.05306569356524</v>
+        <v>50.44540258681773</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>29.67812204518232</v>
+        <v>20.02468010761978</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.566045437400861</v>
+        <v>0.8085355914330724</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.3021702770154608</v>
+        <v>3.816741347240294</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6550</v>
+        <v>6510</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>426.2610618352083</v>
+        <v>431.9468980332318</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>13.7</v>
+        <v>3320</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.2847837048225</v>
+        <v>47.99334809676097</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>24.43703645144781</v>
+        <v>16.91817181243905</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.213693921029051</v>
+        <v>0.4280805604603976</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2022542101247936</v>
+        <v>-19.1046736389584</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6792</v>
+        <v>6670</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>424.3338008327174</v>
+        <v>430.5053902882127</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>66.7</v>
+        <v>259</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.9965053272785</v>
+        <v>45.48323280946506</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.74182418300588</v>
+        <v>24.7873940314838</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.302774101517127</v>
+        <v>0.4470325742187998</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.4179584540680167</v>
+        <v>-2.901989469333766</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6735</v>
+        <v>6803</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>417.7705361120986</v>
+        <v>429.4164385005847</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>279</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.34166143300374</v>
+        <v>33.05306569356524</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.36636780177899</v>
+        <v>29.67812204518232</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3341292959012198</v>
+        <v>2.566045437400861</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0421853338602264</v>
+        <v>-0.3021702770154608</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6597</v>
+        <v>6550</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>411.3234668255387</v>
+        <v>426.2610618352083</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>13.7</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.21078778333123</v>
+        <v>48.2847837048225</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.67983164284999</v>
+        <v>24.43703645144781</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1403860058957672</v>
+        <v>1.213693921029051</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.4396649777106023</v>
+        <v>0.2022542101247936</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6591</v>
+        <v>6792</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>406.2201079439201</v>
+        <v>424.3338008327174</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>55.3</v>
+        <v>66.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.11043131250973</v>
+        <v>51.9965053272785</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.02952486504746</v>
+        <v>22.74182418300588</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.555377217881148</v>
+        <v>1.302774101517127</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.06361224122507859</v>
+        <v>-0.4179584540680167</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6512</v>
+        <v>6735</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>397.6765721692701</v>
+        <v>417.7705361120986</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.35</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.34560953378646</v>
+        <v>41.34166143300374</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9.580883996964308</v>
+        <v>10.36636780177899</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3698481917439916</v>
+        <v>0.3341292959012198</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5050717476504822</v>
+        <v>0.0421853338602264</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6811</v>
+        <v>6597</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>389.4292263968371</v>
+        <v>411.3234668255387</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>222</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.58908769588246</v>
+        <v>48.21078778333123</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.42201325933559</v>
+        <v>11.67983164284999</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.258766415276952</v>
+        <v>0.1403860058957672</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.534263599283572</v>
+        <v>-0.4396649777106023</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6679</v>
+        <v>6591</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>384.3147062141804</v>
+        <v>406.2201079439201</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>269.5</v>
+        <v>55.3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.09477877013262</v>
+        <v>51.11043131250973</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.45252533735326</v>
+        <v>20.02952486504746</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5971535668077383</v>
+        <v>1.555377217881148</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2384123329931702</v>
+        <v>0.06361224122507859</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6830</v>
+        <v>6512</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>377.64610472669</v>
+        <v>397.6765721692701</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>455</v>
+        <v>20.35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.58357604865856</v>
+        <v>52.34560953378646</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>23.59756473952865</v>
+        <v>9.580883996964308</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6914008291003416</v>
+        <v>0.3698481917439916</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-3.672553225495527</v>
+        <v>-0.5050717476504822</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6655</v>
+        <v>6811</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>367.4621317048341</v>
+        <v>389.4292263968371</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.40915383285158</v>
+        <v>52.58908769588246</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9.864948879800099</v>
+        <v>19.42201325933559</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.201378227290307</v>
+        <v>1.258766415276952</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>1.853525287080702</v>
+        <v>-1.534263599283572</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6763</v>
+        <v>6679</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>367.3821864032778</v>
+        <v>384.3147062141804</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>47.05</v>
+        <v>269.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.11414065277034</v>
+        <v>44.09477877013262</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.66386897424725</v>
+        <v>17.45252533735326</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6179413605199683</v>
+        <v>0.5971535668077383</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0813841560933687</v>
+        <v>-0.2384123329931702</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6756</v>
+        <v>6830</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>366.2236180428035</v>
+        <v>377.64610472669</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>101</v>
+        <v>455</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.60955347526883</v>
+        <v>34.58357604865856</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.92842307034961</v>
+        <v>23.59756473952865</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.058376892051893</v>
+        <v>0.6914008291003416</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.3919403244727584</v>
+        <v>-3.672553225495527</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6823</v>
+        <v>6655</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>350.342690377767</v>
+        <v>367.4621317048341</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.80099260807046</v>
+        <v>50.40915383285158</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.91903845466866</v>
+        <v>9.864948879800099</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6908850246770594</v>
+        <v>1.201378227290307</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.665265156165054</v>
+        <v>1.853525287080702</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6624</v>
+        <v>6763</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>349.5720451987341</v>
+        <v>367.3821864032778</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>45.1</v>
+        <v>47.05</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.5419450586359</v>
+        <v>51.11414065277034</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9.626915786706505</v>
+        <v>16.66386897424725</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.775399378847334</v>
+        <v>0.6179413605199683</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.598286810202678</v>
+        <v>-0.0813841560933687</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6498</v>
+        <v>6756</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>348.4956118267642</v>
+        <v>366.2236180428035</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>101</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.56924703467612</v>
+        <v>53.60955347526883</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.43926103996268</v>
+        <v>19.92842307034961</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.268872196298872</v>
+        <v>1.058376892051893</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.080716569180891</v>
+        <v>-0.3919403244727584</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6788</v>
+        <v>6823</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>346.8709434211829</v>
+        <v>350.342690377767</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>445</v>
+        <v>71</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,49 +4792,49 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>53.69323498513376</v>
+        <v>49.80099260807046</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8.247180370197089</v>
+        <v>17.91903845466866</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6010299488773717</v>
+        <v>0.6908850246770594</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.5397073898869245</v>
+        <v>0.665265156165054</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6741</v>
+        <v>6624</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>344.0220383665105</v>
+        <v>349.5720451987341</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>61</v>
+        <v>45.1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.98451604133143</v>
+        <v>52.5419450586359</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.581861825746271</v>
+        <v>9.626915786706505</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5622873443868307</v>
+        <v>1.775399378847334</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1091483258444356</v>
+        <v>1.598286810202678</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6690</v>
+        <v>6498</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>342.2334283011086</v>
+        <v>348.4956118267642</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>168.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.99286251299979</v>
+        <v>42.56924703467612</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.69702418058552</v>
+        <v>20.43926103996268</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6497707292068531</v>
+        <v>0.268872196298872</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.307504406786442</v>
+        <v>-1.080716569180891</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6530</v>
+        <v>6788</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>341.8667904053842</v>
+        <v>346.8709434211829</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>87.8</v>
+        <v>445</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>40.13558266689072</v>
+        <v>53.69323498513376</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.72084685357995</v>
+        <v>8.247180370197089</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7936229532929074</v>
+        <v>0.6010299488773717</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.6518326023825978</v>
+        <v>0.5397073898869245</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6541</v>
+        <v>6741</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>313.7291769070599</v>
+        <v>344.0220383665105</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>41.4</v>
+        <v>61</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.1055114082825</v>
+        <v>44.98451604133143</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.16823090052752</v>
+        <v>8.581861825746271</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.037393343547786</v>
+        <v>0.5622873443868307</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.07409019528398481</v>
+        <v>-0.1091483258444356</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6570</v>
+        <v>6690</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>298.1090604896763</v>
+        <v>342.2334283011086</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>53.8</v>
+        <v>168.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.1940893275573</v>
+        <v>46.99286251299979</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.97178866062654</v>
+        <v>17.69702418058552</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8342247635747401</v>
+        <v>0.6497707292068531</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.4749638290575522</v>
+        <v>-1.307504406786442</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6532</v>
+        <v>6530</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>288.539491702368</v>
+        <v>341.8667904053842</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.82592945985734</v>
+        <v>40.13558266689072</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.13424842061558</v>
+        <v>24.72084685357995</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4190708996447912</v>
+        <v>0.7936229532929074</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.4245445491399495</v>
+        <v>-0.6518326023825978</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6821</v>
+        <v>6541</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>284.8985600701416</v>
+        <v>313.7291769070599</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>60.5</v>
+        <v>41.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.51815617945395</v>
+        <v>53.1055114082825</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.79767598643914</v>
+        <v>16.16823090052752</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3375083184381589</v>
+        <v>1.037393343547786</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.7609872065770246</v>
+        <v>-0.07409019528398481</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6692</v>
+        <v>6570</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>278.2371923169298</v>
+        <v>298.1090604896763</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25.55</v>
+        <v>53.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.00004124962366</v>
+        <v>53.1940893275573</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.28373925615229</v>
+        <v>22.97178866062654</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1438692254242509</v>
+        <v>0.8342247635747401</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1000322427157588</v>
+        <v>-0.4749638290575522</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6504</v>
+        <v>6532</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>276.4628397478195</v>
+        <v>288.539491702368</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>36.25</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.83679249459385</v>
+        <v>49.82592945985734</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.87097436306004</v>
+        <v>15.13424842061558</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.053116441832568</v>
+        <v>0.4190708996447912</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.11014757708698</v>
+        <v>0.4245445491399495</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6606</v>
+        <v>6821</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>275.7035033821923</v>
+        <v>284.8985600701416</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>24.95</v>
+        <v>60.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.73073331295118</v>
+        <v>45.51815617945395</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.8380289237764</v>
+        <v>15.79767598643914</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3639516258589216</v>
+        <v>0.3375083184381589</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0678685204672691</v>
+        <v>-0.7609872065770246</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6722</v>
+        <v>6692</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>272.1652593472803</v>
+        <v>278.2371923169298</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>34.75</v>
+        <v>25.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.42316219530024</v>
+        <v>41.00004124962366</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>33.19951884281555</v>
+        <v>14.28373925615229</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2393036543002649</v>
+        <v>0.1438692254242509</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.2540626969046696</v>
+        <v>0.1000322427157588</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6534</v>
+        <v>6504</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>270.9697090319718</v>
+        <v>276.4628397478195</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>36.25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.35598385546286</v>
+        <v>45.83679249459385</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.87644125648319</v>
+        <v>16.87097436306004</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3721724675641568</v>
+        <v>1.053116441832568</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.007890135988908</v>
+        <v>0.11014757708698</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6789</v>
+        <v>6606</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>264.3215870352963</v>
+        <v>275.7035033821923</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>528</v>
+        <v>24.95</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>52.32575145537279</v>
+        <v>43.73073331295118</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.00917222197326</v>
+        <v>15.8380289237764</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5166785871119598</v>
+        <v>0.3639516258589216</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>1.75882013116793</v>
+        <v>-0.0678685204672691</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6771</v>
+        <v>6722</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>263.5736242857505</v>
+        <v>272.1652593472803</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>39.1</v>
+        <v>34.75</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.97326492527542</v>
+        <v>35.42316219530024</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.35310697581805</v>
+        <v>33.19951884281555</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3204614645088928</v>
+        <v>0.2393036543002649</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2046925283351754</v>
+        <v>-0.2540626969046696</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6768</v>
+        <v>6534</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>257.0205179902943</v>
+        <v>270.9697090319718</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>73.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>28.79860372842815</v>
+        <v>43.35598385546286</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>24.01590874742499</v>
+        <v>11.87644125648319</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5561494552046953</v>
+        <v>0.3721724675641568</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.854842614463011</v>
+        <v>-0.007890135988908</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6805</v>
+        <v>6789</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>256.6130778524931</v>
+        <v>264.3215870352963</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1630</v>
+        <v>528</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.28561853713987</v>
+        <v>52.32575145537279</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.17956335562084</v>
+        <v>14.00917222197326</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8136032384979052</v>
+        <v>0.5166785871119598</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-11.08010709560455</v>
+        <v>1.75882013116793</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6561</v>
+        <v>6771</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>251.9089791308019</v>
+        <v>263.5736242857505</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>339.5</v>
+        <v>39.1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.64015707716638</v>
+        <v>35.97326492527542</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.01500200910221</v>
+        <v>23.35310697581805</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7197605252000976</v>
+        <v>0.3204614645088928</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0416562009280605</v>
+        <v>-0.2046925283351754</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6592</v>
+        <v>6768</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>251.5463815975338</v>
+        <v>257.0205179902943</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>61.3</v>
+        <v>73.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.17468230446116</v>
+        <v>28.79860372842815</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>29.87256632859676</v>
+        <v>24.01590874742499</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.147630439552044</v>
+        <v>0.5561494552046953</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.7576857048391432</v>
+        <v>-1.854842614463011</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6533</v>
+        <v>6805</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>241.5158056792061</v>
+        <v>256.6130778524931</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>200</v>
+        <v>1630</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.73506528121796</v>
+        <v>40.28561853713987</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.84577827551739</v>
+        <v>16.17956335562084</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7762803967695129</v>
+        <v>0.8136032384979052</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.4015043801819891</v>
+        <v>-11.08010709560455</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6657</v>
+        <v>6561</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>237.9221984305997</v>
+        <v>251.9089791308019</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>37.15</v>
+        <v>339.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.54144072803707</v>
+        <v>46.64015707716638</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.03312301461947</v>
+        <v>19.01500200910221</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.149214588377378</v>
+        <v>0.7197605252000976</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.2785928505195602</v>
+        <v>0.0416562009280605</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6708</v>
+        <v>6592</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>236.8250930905282</v>
+        <v>251.5463815975337</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>39.8</v>
+        <v>61.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.8194846382378</v>
+        <v>43.17468230446116</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.97436023581703</v>
+        <v>29.87256632859676</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6993321597228044</v>
+        <v>1.147630439552044</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0534942221200763</v>
+        <v>-0.7576857048391432</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6761</v>
+        <v>6533</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>223.1953091288409</v>
+        <v>241.5158056792061</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.19463621582945</v>
+        <v>44.73506528121796</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.92301202846283</v>
+        <v>10.84577827551739</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5873060682944333</v>
+        <v>0.7762803967695129</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.9173414531130232</v>
+        <v>0.4015043801819891</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6605</v>
+        <v>6657</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>216.7997394304353</v>
+        <v>237.9221984305997</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>137.5</v>
+        <v>37.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.95014162525231</v>
+        <v>51.54144072803707</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.57857138991127</v>
+        <v>21.03312301461947</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9151793574633248</v>
+        <v>1.149214588377378</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.075849836661511</v>
+        <v>0.2785928505195602</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6577</v>
+        <v>6708</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>214.0861763967464</v>
+        <v>236.8250930905282</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>39.8</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.9692920226837</v>
+        <v>46.8194846382378</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.27402385025219</v>
+        <v>14.97436023581703</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2478859024717916</v>
+        <v>0.6993321597228044</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1460981913112224</v>
+        <v>0.0534942221200763</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6581</v>
+        <v>6761</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>202.7041689849868</v>
+        <v>223.1953091288409</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>106.5</v>
+        <v>198</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.31892640889672</v>
+        <v>50.19463621582945</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.33629296178135</v>
+        <v>14.92301202846283</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6575074805016433</v>
+        <v>0.5873060682944333</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.2045697402957518</v>
+        <v>-0.9173414531130232</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6598</v>
+        <v>6605</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>199.4257360040483</v>
+        <v>216.7997394304353</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23.05</v>
+        <v>137.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.50829761317999</v>
+        <v>48.95014162525231</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.70517011400553</v>
+        <v>13.57857138991127</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.304008530267053</v>
+        <v>0.9151793574633248</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1481696860260403</v>
+        <v>-1.075849836661511</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6776</v>
+        <v>6577</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>192.4741028720535</v>
+        <v>214.0861763967464</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>54.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>37.56538123352696</v>
+        <v>41.9692920226837</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.82847371892289</v>
+        <v>22.27402385025219</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5170021374758111</v>
+        <v>0.2478859024717916</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.4836850167253894</v>
+        <v>-0.1460981913112224</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6680</v>
+        <v>6581</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>186.8881767150668</v>
+        <v>202.7041689849868</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>50.8</v>
+        <v>106.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.909363389941</v>
+        <v>43.31892640889672</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>4.325635040686259</v>
+        <v>12.33629296178135</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2176864507843317</v>
+        <v>0.6575074805016433</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2936529639462873</v>
+        <v>-0.2045697402957518</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6835</v>
+        <v>6598</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>186.7014460142984</v>
+        <v>199.4257360040483</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>34.85</v>
+        <v>23.05</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>35.50819737900545</v>
+        <v>41.50829761317999</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>25.40403098323733</v>
+        <v>19.70517011400553</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6784031983233815</v>
+        <v>1.304008530267053</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1418208322397639</v>
+        <v>-0.1481696860260403</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6671</v>
+        <v>6776</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>175.5589586410636</v>
+        <v>192.4741028720535</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>24.5</v>
+        <v>54.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>29.8870393534864</v>
+        <v>37.56538123352696</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>29.95084951986954</v>
+        <v>18.82847371892289</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4799993122603209</v>
+        <v>0.5170021374758111</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0458056934630839</v>
+        <v>-0.4836850167253894</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6546</v>
+        <v>6680</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>175.3420205514459</v>
+        <v>186.8881767150668</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.99625475030727</v>
+        <v>50.909363389941</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.1026651125533</v>
+        <v>4.325635040686259</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6425253326371065</v>
+        <v>0.2176864507843317</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.4866654441374241</v>
+        <v>0.2936529639462873</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6689</v>
+        <v>6835</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>170.9358020653731</v>
+        <v>186.7014460142984</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>63.9</v>
+        <v>34.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.93786668449444</v>
+        <v>35.50819737900545</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.48262726328496</v>
+        <v>25.40403098323733</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5331767658218545</v>
+        <v>0.6784031983233815</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.3927358569544381</v>
+        <v>-0.1418208322397639</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6720</v>
+        <v>6671</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.9413244356883</v>
+        <v>175.5589586410636</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>144</v>
+        <v>24.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>47.58780242153225</v>
+        <v>29.8870393534864</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>27.85420316592105</v>
+        <v>29.95084951986954</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.469012493573232</v>
+        <v>0.4799993122603209</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.9162999036732128</v>
+        <v>0.0458056934630839</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6674</v>
+        <v>6546</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>150.3877178076859</v>
+        <v>175.3420205514459</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>17</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.78324753014406</v>
+        <v>46.99625475030727</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.29830311048492</v>
+        <v>14.1026651125533</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6942986451774268</v>
+        <v>0.6425253326371065</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0273986599202827</v>
+        <v>-0.4866654441374241</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6552</v>
+        <v>6689</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>137.3088703343707</v>
+        <v>170.9358020653731</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>31.05</v>
+        <v>63.9</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>51.23494231355586</v>
+        <v>39.93786668449444</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.53801561508294</v>
+        <v>16.48262726328496</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7544630258601513</v>
+        <v>0.5331767658218545</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0174056003951947</v>
+        <v>-0.3927358569544381</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6840</v>
+        <v>6720</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>136.4413467125662</v>
+        <v>158.9413244356883</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>65.2</v>
+        <v>144</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>51.03259801826528</v>
+        <v>47.58780242153225</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.30279306600083</v>
+        <v>27.85420316592105</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6704509932081048</v>
+        <v>1.469012493573232</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.1777739816968639</v>
+        <v>0.9162999036732128</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6706</v>
+        <v>6674</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>124.8092040054077</v>
+        <v>150.3877178076859</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.12722379635014</v>
+        <v>42.78324753014406</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.57972458065661</v>
+        <v>19.29830311048492</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5769988003151575</v>
+        <v>0.6942986451774268</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.779272316483572</v>
+        <v>-0.0273986599202827</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6796</v>
+        <v>6552</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>104.0805080328648</v>
+        <v>137.3088703343707</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>60.5</v>
+        <v>31.05</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.45722419285768</v>
+        <v>51.23494231355586</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>25.69614827415851</v>
+        <v>12.53801561508294</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.789152962490661</v>
+        <v>0.7544630258601513</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.3677616235118131</v>
+        <v>-0.0174056003951947</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6838</v>
+        <v>6840</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>93.40364705182731</v>
+        <v>136.4413467125662</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>24.85</v>
+        <v>65.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.64191176993396</v>
+        <v>51.03259801826528</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.84183522742083</v>
+        <v>13.30279306600083</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.440564283827909</v>
+        <v>0.6704509932081048</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0894036839009434</v>
+        <v>-0.1777739816968639</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6807</v>
+        <v>6706</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>85.98939979691495</v>
+        <v>124.8092040054077</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>33.2</v>
+        <v>154</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.4990746807432</v>
+        <v>44.12722379635014</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>16.72372491025452</v>
+        <v>16.57972458065661</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4317433832167274</v>
+        <v>0.5769988003151575</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,62 +6930,221 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.09369654268021339</v>
+        <v>-1.779272316483572</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
+        <v>6796</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>晉弘</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>104.0805080328648</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>52.45722419285768</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>25.69614827415851</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.789152962490661</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.3677616235118131</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>6838</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>台新藥</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>93.40364705182731</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>50.64191176993396</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>12.84183522742083</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>1.440564283827909</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.0894036839009434</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6807</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>峰源-KY</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>85.98939979691495</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>44.4990746807432</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>16.72372491025452</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.4317433832167274</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.09369654268021339</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
         <v>6558</v>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>興能高</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>84.90695082328033</v>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E126" s="2" t="n">
         <v>30.4</v>
       </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
         <v>49.9565586622074</v>
       </c>
-      <c r="I123" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>19.46528697169759</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J126" s="2" t="n">
         <v>0.9554417132155058</v>
       </c>
-      <c r="K123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
         <v>-0.0813106844443047</v>
       </c>
-      <c r="O123" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, obv_uptrend</t>
         </is>
